--- a/EIANN/data/FigT6_mnist_hyperparams_part3.xlsx
+++ b/EIANN/data/FigT6_mnist_hyperparams_part3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,172 +436,114 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Feedforward ANN 
-(no hidden)</t>
+          <t>Backprop</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Feedforward ANN 
-(learned bias)</t>
+          <t>Backprop (EIANN)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Feedforward ANN 
-(no bias)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Backprop (EIANN)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Dendritic 
-Target Propagation</t>
+          <t>Dend Target Prop</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Winit (Output)</t>
+          <t>Winit (H1)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.386548065293654</v>
+        <v>1.558512143768813</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5433568834277912</v>
+        <v>0.346349702292413</v>
       </c>
       <c r="D2" t="n">
-        <v>3.518843703166975</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5.977812184651836</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.42693091561223</v>
+        <v>1.251580156442688</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wη (Output)</t>
+          <t>Wη (H1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08158367762594287</v>
+        <v>0.03782664606215736</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01080926960544266</v>
+        <v>0.1605450544174098</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001309333856710242</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6722278010177094</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.09769059583309837</v>
+        <v>0.004531157096362757</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Winit (H1)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Winit (H2)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4498740230022448</v>
       </c>
       <c r="C4" t="n">
-        <v>3.092179371471005</v>
+        <v>1.915958110976723</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7661562722497335</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.327218040830208</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.744225231975699</v>
+        <v>0.9847368481970282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wη (H1)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Wη (H2)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.03782664606215736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2344242206840233</v>
+        <v>0.1605450544174098</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008671959543266558</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1769523365865042</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.08563556008428913</v>
+        <v>0.004531157096362757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Winit (H2)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Winit (Output)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.13336059534409</v>
       </c>
       <c r="C6" t="n">
-        <v>1.068480127016743</v>
+        <v>1.374462932196516</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1340356807870724</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5.183393888582326</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.396275790739738</v>
+        <v>0.8454280535376003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wη (H2)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Wη (Output)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03239456848079787</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2344242206840233</v>
+        <v>0.04675558581255138</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008671959543266558</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.1769523365865042</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.08563556008428913</v>
+        <v>0.04104131109100031</v>
       </c>
     </row>
     <row r="8">
@@ -615,21 +557,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4.708083116173457</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.717071876658599</v>
+      <c r="C8" t="n">
+        <v>0.3793775999178492</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06480172290199618</v>
       </c>
     </row>
     <row r="9">
@@ -643,21 +575,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1.064629862199998</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8.526807327982732</v>
+      <c r="C9" t="n">
+        <v>0.2345638479590626</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.619731630253789</v>
       </c>
     </row>
     <row r="10">
@@ -671,21 +593,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.7308804739762219</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.5572584153779</v>
+      <c r="C10" t="n">
+        <v>0.2648889193438002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.862543520783099</v>
       </c>
     </row>
     <row r="11">
@@ -699,21 +611,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1.985595933356355</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3.821257280968513</v>
+      <c r="C11" t="n">
+        <v>1.168135903500541</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.216435902953786</v>
       </c>
     </row>
     <row r="12">
@@ -727,21 +629,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3.273971082147326</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.961562817177921</v>
+      <c r="C12" t="n">
+        <v>1.192526471534233</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8497135201709712</v>
       </c>
     </row>
     <row r="13">
@@ -755,21 +647,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3.386558310279101</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3.356842824473377</v>
+      <c r="C13" t="n">
+        <v>2.328515327357697</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.294067777368571</v>
       </c>
     </row>
     <row r="14">
@@ -783,21 +665,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.6920399968903772</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.672772790852625</v>
+      <c r="C14" t="n">
+        <v>0.4180524516667432</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.123538333576148</v>
       </c>
     </row>
     <row r="15">
@@ -811,21 +683,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1.656403773484931</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.527793096667097</v>
+      <c r="C15" t="n">
+        <v>1.29514552081384</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9621337779958217</v>
       </c>
     </row>
     <row r="16">
@@ -839,21 +701,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1.762993057568605</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.114662304188637</v>
+      <c r="C16" t="n">
+        <v>0.773126187876416</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9370545344944556</v>
       </c>
     </row>
     <row r="17">
@@ -867,21 +719,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2.289938249676595</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.982369341320862</v>
+      <c r="C17" t="n">
+        <v>1.862098997069794</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6709133243700003</v>
       </c>
     </row>
     <row r="18">
@@ -895,21 +737,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.460040157290248</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9622943352611545</v>
+      <c r="C18" t="n">
+        <v>1.532746399058863</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1802509449834768</v>
       </c>
     </row>
     <row r="19">
@@ -923,21 +755,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1.559187825960845</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3.924537045484193</v>
+      <c r="C19" t="n">
+        <v>1.404644552125373</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.004975359985889</v>
       </c>
     </row>
     <row r="20">
@@ -956,18 +778,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.7284678918500063</v>
+      <c r="D20" t="n">
+        <v>0.4334951600841279</v>
       </c>
     </row>
     <row r="21">
@@ -986,18 +798,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.2101712344149589</v>
+      <c r="D21" t="n">
+        <v>0.2461096190302813</v>
       </c>
     </row>
     <row r="22">
@@ -1016,18 +818,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.1879267248852734</v>
+      <c r="D22" t="n">
+        <v>0.3117506142233962</v>
       </c>
     </row>
     <row r="23">
@@ -1046,18 +838,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.08025562647850921</v>
+      <c r="D23" t="n">
+        <v>0.1108223135685588</v>
       </c>
     </row>
     <row r="24">
@@ -1076,18 +858,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>9.419321612663568</v>
+      <c r="D24" t="n">
+        <v>4.659467073640639</v>
       </c>
     </row>
     <row r="25">
@@ -1106,18 +878,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.01343573403768564</v>
+      <c r="D25" t="n">
+        <v>0.05657747249822739</v>
       </c>
     </row>
     <row r="26">
@@ -1136,18 +898,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1.171246432090221</v>
+      <c r="D26" t="n">
+        <v>2.867312408536833</v>
       </c>
     </row>
     <row r="27">
@@ -1166,18 +918,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2.713538702536155</v>
+      <c r="D27" t="n">
+        <v>0.9920090582938009</v>
       </c>
     </row>
     <row r="28">
@@ -1196,18 +938,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0.2101712344149589</v>
+      <c r="D28" t="n">
+        <v>0.2461096190302813</v>
       </c>
     </row>
     <row r="29">
@@ -1226,18 +958,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.7149623055734934</v>
+      <c r="D29" t="n">
+        <v>1.698155094848647</v>
       </c>
     </row>
     <row r="30">
@@ -1256,18 +978,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.08025562647850921</v>
+      <c r="D30" t="n">
+        <v>0.1108223135685588</v>
       </c>
     </row>
     <row r="31">
@@ -1286,18 +998,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>11.68995252240356</v>
+      <c r="D31" t="n">
+        <v>33.33551016260789</v>
       </c>
     </row>
     <row r="32">
@@ -1316,18 +1018,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.01343573403768564</v>
+      <c r="D32" t="n">
+        <v>0.05657747249822739</v>
       </c>
     </row>
     <row r="33">
@@ -1346,18 +1038,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>2.147366810208358</v>
+      <c r="D33" t="n">
+        <v>3.893661256381292</v>
       </c>
     </row>
   </sheetData>

--- a/EIANN/data/FigT6_mnist_hyperparams_part3.xlsx
+++ b/EIANN/data/FigT6_mnist_hyperparams_part3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,31 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Backprop</t>
+          <t>BTSP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Backprop (EIANN)</t>
+          <t>LDS, 
+fixed top-down</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Dend Target Prop</t>
+          <t>LDS, 
+learned top-down</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BTSP, 
+fixed top-down</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>BTSP, 
+learned top-down</t>
         </is>
       </c>
     </row>
@@ -457,589 +471,1041 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.558512143768813</v>
+        <v>3.523743232390591</v>
       </c>
       <c r="C2" t="n">
-        <v>0.346349702292413</v>
+        <v>1.507301303453382</v>
       </c>
       <c r="D2" t="n">
-        <v>1.251580156442688</v>
+        <v>1.334544098018755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.982054676122692</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.61727120337632</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wη (H1)</t>
+          <t>η, W (H1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03782664606215736</v>
+        <v>0.01009938235093999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1605450544174098</v>
+        <v>0.01710810722072439</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004531157096362757</v>
+        <v>0.0177579447045343</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.002499955095692264</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.008046168178811415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Winit (H2)</t>
+          <t>BTSP λ (H1)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4498740230022448</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.915958110976723</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9847368481970282</v>
+        <v>0.01616643098277037</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0157582773371946</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03684490706695098</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wη (H2)</t>
+          <t>BTSP Wmax (H1)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03782664606215736</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1605450544174098</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.004531157096362757</v>
+        <v>0.3520096518599288</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3066727862308647</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3847974178096945</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Winit (Output)</t>
+          <t>Yinit (SomaI, H1)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.13336059534409</v>
+        <v>2.196024886031613</v>
       </c>
       <c r="C6" t="n">
-        <v>1.374462932196516</v>
+        <v>0.7135693808213259</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8454280535376003</v>
+        <v>1.1994926797055</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9457871075285322</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9531247877367462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wη (Output)</t>
+          <t>Yinit (DendI, H1)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03239456848079787</v>
+        <v>1.430906888361427</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04675558581255138</v>
+        <v>0.105932882455874</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04104131109100031</v>
+        <v>0.9117181280320573</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8044728940788499</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6643757499571086</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H1)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, Y (DendI, H1)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.05396663369038972</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3793775999178492</v>
+        <v>0.03827862359817637</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06480172290199618</v>
+        <v>0.1806346990823588</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0136790009621945</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03203500727860572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H1)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.2345638479590626</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.619731630253789</v>
+          <t>Bscale (H1)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1533853976084567</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H1)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Winit (SomaI, H1)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.20871096114297</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2648889193438002</v>
+        <v>2.87375364236587</v>
       </c>
       <c r="D10" t="n">
-        <v>0.862543520783099</v>
+        <v>0.9968362476919066</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.64308664636432</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.939248217194782</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H1)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Qinit (SomaI, H1)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7035747473578501</v>
       </c>
       <c r="C11" t="n">
-        <v>1.168135903500541</v>
+        <v>0.8390095918853383</v>
       </c>
       <c r="D11" t="n">
-        <v>1.216435902953786</v>
+        <v>0.3448860213154623</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3386432747185851</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3795650168540203</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H2)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rinit (SomaI, H1)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.184776146596312</v>
       </c>
       <c r="C12" t="n">
-        <v>1.192526471534233</v>
+        <v>1.269005590827135</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8497135201709712</v>
+        <v>0.8168111262978619</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8937830285936182</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8944540089568928</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H2)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, Q (DendI, H1)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1476742113118229</v>
       </c>
       <c r="C13" t="n">
-        <v>2.328515327357697</v>
+        <v>0.08588774306220479</v>
       </c>
       <c r="D13" t="n">
-        <v>1.294067777368571</v>
+        <v>0.03046053167219755</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.154468549812171</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.08591883766346817</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H2)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Qsum (DendI, H1)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>22.15103313610746</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4180524516667432</v>
+        <v>9.134061186217822</v>
       </c>
       <c r="D14" t="n">
-        <v>1.123538333576148</v>
+        <v>21.49296580654145</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32.71216432332772</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40.88709705380823</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H2)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, R (DendI, H1)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.05168714041303703</v>
       </c>
       <c r="C15" t="n">
-        <v>1.29514552081384</v>
+        <v>0.005417571574235529</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9621337779958217</v>
+        <v>0.0584269518445007</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.02804196563480635</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1952514389576858</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, Output)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rsum (DendI, H1)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.562437591068871</v>
       </c>
       <c r="C16" t="n">
-        <v>0.773126187876416</v>
+        <v>0.05658286840696301</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9370545344944556</v>
+        <v>4.098353428169238</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.638420080325724</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.239382106113913</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Winit (SomaI, Output)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Winit (H2)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.8324299842972416</v>
       </c>
       <c r="C17" t="n">
-        <v>1.862098997069794</v>
+        <v>1.326063290959874</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6709133243700003</v>
+        <v>0.7726457666473203</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.329371934912368</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.858104784069669</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, Output)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, W (H2)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.01009938235093999</v>
       </c>
       <c r="C18" t="n">
-        <v>1.532746399058863</v>
+        <v>0.01710810722072439</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1802509449834768</v>
+        <v>0.0177579447045343</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.002499955095692264</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.008046168178811415</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, Output)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1.404644552125373</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.004975359985889</v>
+          <t>BTSP λ (H2)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.01616643098277037</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0157582773371946</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.03684490706695098</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H1)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BTSP Wmax (H2)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4407858057651082</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0.4334951600841279</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.384015070242426</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4818425829217644</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yη (DendI, H1)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Yinit (SomaI, H2)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.2761394594186574</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.082710007313077</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2461096190302813</v>
+        <v>0.5476936086638823</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1947782246297449</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2614810628260841</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bscale (H1)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Yinit (DendI, H2)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6.210903692247495</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.011614855758185</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3117506142233962</v>
+        <v>1.169078298332736</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.723399602313551</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.773298041549072</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Qη (DendI, H1)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, Y (DendI, H2)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.05396663369038972</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.03827862359817637</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1108223135685588</v>
+        <v>0.1806346990823588</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0136790009621945</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03203500727860572</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QΣ (DendI, H1)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bscale (H2)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5.949706595354167</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>4.659467073640639</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rη (DendI, H1)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Winit (SomaI, H2)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.47560165143195</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.004752016359149</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05657747249822739</v>
+        <v>0.927916368001388</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.516306753810923</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.371326948926786</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RΣ (DendI, H1)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Qinit (SomaI, H2)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.3042252089830038</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.01300788814266146</v>
       </c>
       <c r="D26" t="n">
-        <v>2.867312408536833</v>
+        <v>0.3694170320882082</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4541198332019962</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.732967996345794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H2)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rinit (SomaI, H2)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.003267387530705</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.775005180527675</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9920090582938009</v>
+        <v>0.8261503140716505</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.184330772628778</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.027422794604548</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Yη (DendI, H2)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, Q (DendI, H2)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.1476742113118229</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.08588774306220479</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2461096190302813</v>
+        <v>0.03046053167219755</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.154468549812171</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.08591883766346817</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bscale (H2)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Qsum (DendI, H2)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>53.45959910048472</v>
+      </c>
+      <c r="C29" t="n">
+        <v>17.23632332569193</v>
       </c>
       <c r="D29" t="n">
-        <v>1.698155094848647</v>
+        <v>19.82065350174418</v>
+      </c>
+      <c r="E29" t="n">
+        <v>49.73261611643169</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15.23915634263287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Qη (DendI, H2)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, R (DendI, H2)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.05168714041303703</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.005417571574235529</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1108223135685588</v>
+        <v>0.0584269518445007</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.02804196563480635</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1952514389576858</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QΣ (DendI, H2)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rsum (DendI, H2)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.542820522240908</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.582001385877688</v>
       </c>
       <c r="D31" t="n">
-        <v>33.33551016260789</v>
+        <v>4.411104618264799</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.932492378806401</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.295456652036057</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rη (DendI, H2)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Winit (Output)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8.597381937643748</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.4322583592043802</v>
       </c>
       <c r="D32" t="n">
-        <v>0.05657747249822739</v>
+        <v>1.327840684794275</v>
+      </c>
+      <c r="E32" t="n">
+        <v>12.64101900442142</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.95197475563094</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RΣ (DendI, H2)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>η, W (Output)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.02582435747972173</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.02218411174038816</v>
       </c>
       <c r="D33" t="n">
-        <v>3.893661256381292</v>
+        <v>0.01621283923708346</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0290885208879536</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.02737426927685587</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BTSP λ (Output)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.01616643098277037</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0157582773371946</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.03684490706695098</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BTSP Wmax (Output)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.4352661942279872</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5854233958952332</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7401860244727729</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Yinit (SomaI, Output)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.1893001197317992</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.2388401014192067</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.5080345295874349</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2754363120794391</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3089790206264019</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Winit (SomaI, Output)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.134129112297815</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.3644482340286074</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2540890859479009</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.3435796229643</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8116675911567026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Qinit (SomaI, Output)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.1275716533117956</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5277298031223785</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.04138101738915224</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2702678305689406</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.661957263996603</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rinit (SomaI, Output)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.073242600857402</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5435078623704698</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.4425997054641082</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.927882529098529</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.570930265215855</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Binit (H1)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.09590090749427979</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.01328828301643765</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Binit (H2)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1.121848200414685</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2.706580495999002</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>η, B (H1)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.02451114383266021</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.02161182208563309</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bsum (H1)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.353895631904696</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.04671735238615</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>η, B (H2)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.03358952518739206</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.008774217532772287</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Bsum (H2)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.4448458948197402</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5107072942461069</v>
       </c>
     </row>
   </sheetData>
